--- a/data/quizzes.xlsx
+++ b/data/quizzes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="quizzes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quizzes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,166 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>2026-07-03 10:56:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Banking Ops Battle</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IVR</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Banking Ops Battle - IVR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IVR</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:04:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bank-260703-141304</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IVR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IVR</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:13:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Banking Ops Battle</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KPI &amp; Metrics + IVR</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:30:43</t>
         </is>
       </c>
     </row>
@@ -682,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,6 +2415,1731 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>subjective</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>How would you explain 'why KYC matters' to an annoyed customer in one breath?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>45</v>
+      </c>
+      <c r="K33" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>The IVR handled 4700 calls; 3260 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>69.4%</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>81.9%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>72.4%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>64.4%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>30</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The IVR handled 3200 calls; 1711 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>53.5%</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>56.5%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>30</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The IVR handled 2800 calls; 1810 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>64.6%</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>70.1%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>69.6%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>72.6%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>30</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>The IVR handled 4500 calls; 2743 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.5%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>30</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>The IVR handled 1900 calls; 1139 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>63.4%</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>72.4%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>56.9%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>59.9%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>30</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>The IVR handled 1900 calls; 1410 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>82.2%</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>62.2%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>74.2%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>30</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The IVR handled 2700 calls; 2126 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>78.7%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>76.2%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>82.2%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>94.2%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>30</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>What does DNIS stand for?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dialed Number Identification Service</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Barge-In</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Text To Speech</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Voice User Interface</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bank-260703-140125</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Which statement about TTS is TRUE?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TTS means: converting text into spoken audio prompts</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TTS means: share of callers pressing to leave the IVR for an agent</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>TTS means: identifying which number the caller dialled</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TTS means: customer record opening automatically as the call arrives</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>subjective</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>A VIP customer got wrong information yesterday. Draft your callback opening line.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>45</v>
+      </c>
+      <c r="K43" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>What does IVR stand for?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Interactive Voice Response</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Natural Language Understanding (IVR)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Barge-In</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Menu Depth</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>20</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>What does SPOP stand for?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Skill Based Routing</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Automatic Number Identification</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dialed Number Identification Service</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Screen Pop</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Barge-in in an IVR means:</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Callers can respond before the prompt finishes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>IVR hanging up on silence</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Supervisors joining calls</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Agents interrupting customers</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “extracting caller intent from free speech instead of menus”?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NLUI (Natural Language Understanding (IVR))</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TTS (Text To Speech)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CCB (Courtesy Callback)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SBR (Skill Based Routing)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>20</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>What does ANI stand for?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Automatic Number Identification</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Barge-In</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Opt-Out Rate</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Courtesy Callback</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>20</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “caller's phone number captured automatically”?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>IVR (Interactive Voice Response)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>VUI (Voice User Interface)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ANI (Automatic Number Identification)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SPOP (Screen Pop)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>20</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of callers pressing to leave the IVR for an agent”?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DTMF (Dual Tone Multi Frequency)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SBR (Skill Based Routing)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>OPTR (Opt-Out Rate)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>IVR (Interactive Voice Response)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>What does TTS stand for?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Voice User Interface</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skill Based Routing</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Automatic Call Distributor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Text To Speech</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bank-260703-140439</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>9</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “customer record opening automatically as the call arrives”?</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SPOP (Screen Pop)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ASR (Automatic Speech Recognition)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MDEP (Menu Depth)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DTMF (Dual Tone Multi Frequency)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>20</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bank-260703-141304</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>What does VUI stand for?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Dual Tone Multi Frequency</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Voice User Interface</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Courtesy Callback</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Skill Based Routing</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>20</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bank-260703-141304</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>subjective</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>An elderly customer struggles with the mobile app. How would you help without pushing them away from digital?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>45</v>
+      </c>
+      <c r="K54" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bank-260703-141304</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “caller's phone number captured automatically”?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IVR (Interactive Voice Response)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>VUI (Voice User Interface)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ANI (Automatic Number Identification)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SPOP (Screen Pop)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>20</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bank-260703-141304</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A caller says 'I lost my debit card' to the open-ended IVR prompt. Which technology maps this to the card-block flow?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DTMF</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Text To Speech</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Screen pop</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Natural Language Understanding</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>25</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bank-260703-141304</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>What does OPTR stand for?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Voice User Interface</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Courtesy Callback</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Menu Depth</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Opt-Out Rate</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>20</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>An agent handled 40 calls with total talk 7240s, hold 1400s and ACW 1240s. AHT in seconds = ?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>232 sec</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>217 sec</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>307 sec</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>247 sec</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>30</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2500 calls were offered and 345 callers hung up before answer. What is the abandonment rate?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>28.8%</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>13.8%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>30</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1400 calls were offered and 60 callers hung up before answer. What is the abandonment rate?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>30</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>600 calls were offered and 43 callers hung up before answer. What is the abandonment rate?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>7.2%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>30</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>The IVR handled 1700 calls; 664 completed without reaching an agent. Containment rate = ?</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>44.1%</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>36.6%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>30</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>What does NLUI stand for?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Screen Pop</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skill Based Routing</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Natural Language Understanding (IVR)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Dialed Number Identification Service</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>20</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>900 calls were offered and 62 callers hung up before answer. What is the abandonment rate?</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>30</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>An agent was scheduled 144 hours this month; 36 hours went to leave, training and breaks. Shrinkage = ?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>30</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>8</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>In an NPS survey, 56% were promoters, 5% detractors and the rest passives. NPS = ?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>30</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bank-260703-143043</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>9</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>What does ANI stand for?</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Automatic Number Identification</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Barge-In</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Opt-Out Rate</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Courtesy Callback</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>20</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quizzes.xlsx
+++ b/data/quizzes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quizzes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="quizzes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,22 +474,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citi Trivia &amp; Team Fun</t>
+          <t>Banking Ops Battle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🎬</t>
+          <t>🏦</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>KPI &amp; Metrics + IVR</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,38 +502,38 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>host@abc.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-02 22:43:58</t>
+          <t>2026-07-04 00:36:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Citi History &amp; Values Sprint</t>
+          <t>Banking Ops Battle 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>💼</t>
+          <t>🏦</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Trivia</t>
+          <t>KPI &amp; Metrics + IVR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -542,38 +542,38 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>host@abc.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-02 22:43:59</t>
+          <t>2026-07-04 00:36:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>emoji-movies</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emoji Movie Puzzles</t>
+          <t>ABC Company Trivia &amp; Team Fun</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🧩</t>
+          <t>🎬</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Picture Round</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -587,33 +587,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-02 22:44:00</t>
+          <t>2026-07-04 09:47:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bank-260702-225447</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VoteTest</t>
+          <t>ABC Company History &amp; Values Sprint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🏦</t>
+          <t>💼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KPI &amp; Metrics</t>
+          <t>Trivia</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -622,38 +622,38 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-02 22:54:47</t>
+          <t>2026-07-04 09:48:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>emoji-movies</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banking Ops Battle</t>
+          <t>Emoji Movie Puzzles</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🏦</t>
+          <t>🧩</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Picture Round</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -662,34 +662,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>admin@citi.com</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-03 10:56:49</t>
+          <t>2026-07-04 09:48:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>import-260704-191455</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banking Ops Battle</t>
+          <t>Imported Quiz Pack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🏦</t>
+          <t>📦</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IVR</t>
+          <t>Imported</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -702,132 +702,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>admin@citi.com</t>
+          <t>host@abc.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-03 14:01:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Banking Ops Battle - IVR</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IVR</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>admin@citi.com</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-07-03 14:04:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bank-260703-141304</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IVR</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>IVR</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>admin@citi.com</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-07-03 14:13:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Banking Ops Battle</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>KPI &amp; Metrics + IVR</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>admin@citi.com</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-07-03 14:30:43</t>
+          <t>2026-07-04 19:14:55</t>
         </is>
       </c>
     </row>
@@ -842,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,11 +781,21 @@
           <t>points</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>media_type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>media_file</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -918,37 +808,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>In which year was Citi (then City Bank of New York) founded?</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1789</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1812</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1865</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1901</v>
+          <t>1100 calls were offered and 159 callers hung up before answer. What is the abandonment rate?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>22.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>29.5%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -961,45 +861,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>What does the red arc in the Citi logo represent?</t>
+          <t>The IVR handled 500 calls; 239 completed without reaching an agent. Containment rate = ?</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A rainbow</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>An umbrella heritage</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A smile</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A bridge</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1012,45 +914,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Which of these is a Citi value?</t>
+          <t>An agent spent 317 minutes handling contacts and 111 minutes waiting. Occupancy = ?</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Move fast, break things</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>We take ownership</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Always be closing</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fail forward</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1063,45 +967,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Roughly how many countries does Citi operate in?</t>
+          <t>500 calls were offered and 74 callers hung up before answer. What is the abandonment rate?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>about 60</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>about 95</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>about 160</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>about 200</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1114,27 +1020,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Which city hosts Citi's global headquarters?</t>
+          <t>The IVR handled 2100 calls; 1074 completed without reaching an agent. Containment rate = ?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,16 +1049,18 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1165,45 +1073,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The 'thank you' rewards program by Citi is called…</t>
+          <t>In an NPS survey, 39% were promoters, 14% detractors and the rest passives. NPS = ?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ThankYou®</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GraciasPoints</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CitiCoins</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MerciMiles</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1216,45 +1126,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Which emoji best describes Friday team calls? 😄</t>
+          <t>Of 1000 answered calls, 633 were answered within the 20-second threshold. Service Level = ?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>😴</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🎉</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>📊</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>All of them, in that order</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>citi-trivia</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1267,49 +1179,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Speed bonus in QuizTok is earned by…</t>
+          <t>1100 calls were offered and 97 callers hung up before answer. What is the abandonment rate?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Answering fast</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Answering last</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Using hints</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bribing the host</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1318,49 +1232,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Citi's ATMs were an industry first in which decade?</t>
+          <t>An agent handled 55 calls with total talk 9515s, hold 1430s and ACW 2695s. AHT in seconds = ?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1950s</t>
+          <t>278 sec</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1970s</t>
+          <t>188 sec</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1990s</t>
+          <t>248 sec</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>263 sec</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003601</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1369,49 +1285,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Which Citi value is about doing what's right?</t>
+          <t>An agent spent 372 minutes handling contacts and 24 minutes waiting. Occupancy = ?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Responsible Finance</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1420,27 +1338,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Citi's mascot in QuizTok is a…</t>
+          <t>120 customers answered the survey; 94 rated 4 or 5. CSAT = ?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Red question mark</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blue owl</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold trophy</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Green frog</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1449,20 +1367,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1471,49 +1391,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The best team quiz strategy is…</t>
+          <t>What does MDEP stand for?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panic</t>
+          <t>Menu Depth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guess everything</t>
+          <t>Courtesy Callback</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Read the question 😉</t>
+          <t>Skill Based Routing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Blame the Wi-Fi</t>
+          <t>Dialed Number Identification Service</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1522,49 +1444,51 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A 🔥 streak in QuizTok resets when you…</t>
+          <t>In an NPS survey, 46% were promoters, 28% detractors and the rest passives. NPS = ?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Answer wrong</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Answer fast</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Win a round</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>High-five</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>citi-history</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1573,49 +1497,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Which one is NOT a QuizTok award?</t>
+          <t>The IVR handled 3300 calls; 2318 completed without reaching an agent. Containment rate = ?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Speed Demon</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longest Streak</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sharp Shooter</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Best Excel Formula</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emoji-movies</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1624,27 +1550,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>🦁👑 = which movie?</t>
+          <t>A team handled 1350 contacts; 938 were resolved on first contact. What is the FCR?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The Lion King</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jungle Book</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Zootopia</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1653,20 +1579,22 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emoji-movies</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1675,49 +1603,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>🕷️🧑 = which hero?</t>
+          <t>540 customers answered the survey; 405 rated 4 or 5. CSAT = ?</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Batman</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ant-Man</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spider-Man</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Iron Man</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emoji-movies</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1726,49 +1656,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>🚢🧊💔 = which movie?</t>
+          <t>340 customers answered the survey; 316 rated 4 or 5. CSAT = ?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Titanic</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Life of Pi</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Poseidon</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
       </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emoji-movies</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1777,49 +1709,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>👽📞🏠 = which classic?</t>
+          <t>The IVR handled 1900 calls; 1410 completed without reaching an agent. Containment rate = ?</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Alien</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>E.T.</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arrival</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Men in Black</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emoji-movies</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1828,111 +1762,157 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>🧙‍♂️💍🌋 = which saga?</t>
+          <t>In an NPS survey, 48% were promoters, 39% detractors and the rest passives. NPS = ?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Narnia</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lord of the Rings</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Eragon</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bank-260702-225447</t>
+          <t>bank-260704-003607</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>subjective</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Describe the perfect handover from chatbot to human agent.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>Of 400 answered calls, 327 were answered within the 20-second threshold. Service Level = ?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>79.2%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>97.2%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>86.8%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="J21" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>300</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bank-260702-225447</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>subjective</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Describe your dream agent-assist screen — what's on it?</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>In which year was ABC Company founded?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>300</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1941,49 +1921,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+          <t>What does the red arc in the ABC Company logo represent?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Explain why the transfers happened</t>
+          <t>A rainbow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Offer compensation straight away</t>
+          <t>An umbrella heritage</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Acknowledge the frustration and own the issue</t>
+          <t>A smile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Transfer to a supervisor immediately</t>
+          <t>A bridge</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1992,32 +1974,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>What does TKT stand for?</t>
+          <t>Which of these is an ABC Company value?</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Soft Skills</t>
+          <t>Move fast, break things</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Empathy Statement</t>
+          <t>We take ownership</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Workforce Management</t>
+          <t>Always be closing</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ticket</t>
+          <t>Fail forward</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2026,15 +2008,17 @@
       <c r="K24" t="n">
         <v>1000</v>
       </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2043,27 +2027,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Which of the following is a genuine benefit of workforce management?</t>
+          <t>Roughly how many countries does ABC Company operate in?</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reports are only generated once a year</t>
+          <t>about 60</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hold time is hidden from reports</t>
+          <t>about 95</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The right number of agents are staffed for forecast volume</t>
+          <t>about 160</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Survey scores below 4 are deleted</t>
+          <t>about 200</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2077,15 +2061,17 @@
       <c r="K25" t="n">
         <v>1000</v>
       </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2094,32 +2080,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Which of the following is a genuine benefit of empathy statements?</t>
+          <t>Which city hosts ABC Company's global headquarters?</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Agents no longer need product knowledge</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Customers feel heard before the fix begins</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>The metric dashboard turns green regardless of performance</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Customers are automatically upsold on every call</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2128,15 +2114,17 @@
       <c r="K26" t="n">
         <v>1000</v>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2145,27 +2133,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+          <t>The 'thank you' rewards program by ABC Company is called…</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ESC (Escalation)</t>
+          <t>ThankYou®</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CTI (Computer Telephony Integration)</t>
+          <t>GraciasPoints</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SRQ (Service Request)</t>
+          <t>AbcCoins</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HOLD (Hold Time)</t>
+          <t>MerciMiles</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2179,46 +2167,70 @@
       <c r="K27" t="n">
         <v>1000</v>
       </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>subjective</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>Which emoji best describes Friday team calls? 😄</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>😴</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>🎉</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>📊</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>All of them, in that order</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="J28" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>300</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-trivia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2227,32 +2239,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+          <t>Speed bonus in QuizTok is earned by…</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PKB (Positive Key Behaviour)</t>
+          <t>Answering fast</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RET (Retention Rate)</t>
+          <t>Answering last</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FLR (First Line Resolution)</t>
+          <t>Using hints</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CSR (Customer Service Representative)</t>
+          <t>Bribing the host</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2261,15 +2273,17 @@
       <c r="K29" t="n">
         <v>1000</v>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2278,49 +2292,51 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+          <t>ABC Company's ATMs were an industry first in which decade?</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PKB (Positive Key Behaviour)</t>
+          <t>1950s</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CBAK (Callback)</t>
+          <t>1970s</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SOFT (Soft Skills)</t>
+          <t>1990s</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WFO (Workforce Optimisation)</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
       </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2329,27 +2345,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>What does WFO stand for?</t>
+          <t>Which ABC Company value is about doing what's right?</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Retention Rate</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Workforce Optimisation</t>
+          <t>Responsible Finance</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>First Line Resolution</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ticket</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2358,20 +2374,22 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
       </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bank-260703-105649</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2380,80 +2398,104 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>What does CLF stand for?</t>
+          <t>ABC Company's mascot in QuizTok is a…</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Voice of the Customer</t>
+          <t>Red question mark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Service Request</t>
+          <t>Blue owl</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Positive Key Behaviour</t>
+          <t>Gold trophy</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Closed Loop Feedback</t>
+          <t>Green frog</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
       </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>subjective</t>
+          <t>mcq</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How would you explain 'why KYC matters' to an annoyed customer in one breath?</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>The best team quiz strategy is…</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Guess everything</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Read the question 😉</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Blame the Wi-Fi</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J33" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>300</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2462,27 +2504,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The IVR handled 4700 calls; 3260 completed without reaching an agent. Containment rate = ?</t>
+          <t>A 🔥 streak in QuizTok resets when you…</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>Answer wrong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>Answer fast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>Win a round</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>High-five</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2491,20 +2533,22 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
       </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>abc-history</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2513,49 +2557,51 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The IVR handled 3200 calls; 1711 completed without reaching an agent. Containment rate = ?</t>
+          <t>Which one is NOT a QuizTok award?</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>Speed Demon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>Longest Streak</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>Sharp Shooter</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>Best Excel Formula</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
       </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>emoji-movies</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2564,49 +2610,51 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>The IVR handled 2800 calls; 1810 completed without reaching an agent. Containment rate = ?</t>
+          <t>🦁👑 = which movie?</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>The Lion King</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>Jungle Book</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>Zootopia</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>emoji-movies</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2615,49 +2663,51 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>The IVR handled 4500 calls; 2743 completed without reaching an agent. Containment rate = ?</t>
+          <t>🕷️🧑 = which hero?</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>Batman</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>Ant-Man</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>Spider-Man</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>Iron Man</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
       </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>emoji-movies</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2666,49 +2716,51 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The IVR handled 1900 calls; 1139 completed without reaching an agent. Containment rate = ?</t>
+          <t>🚢🧊💔 = which movie?</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>Life of Pi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>Poseidon</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
       </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>emoji-movies</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2717,49 +2769,51 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The IVR handled 1900 calls; 1410 completed without reaching an agent. Containment rate = ?</t>
+          <t>👽📞🏠 = which classic?</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>Alien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>E.T.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>Arrival</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>Men in Black</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
       </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>emoji-movies</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2768,49 +2822,51 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>The IVR handled 2700 calls; 2126 completed without reaching an agent. Containment rate = ?</t>
+          <t>🧙‍♂️💍🌋 = which saga?</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>Harry Potter</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>Narnia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>Lord of the Rings</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>Eragon</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
       </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>import-260704-191455</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2819,27 +2875,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>What does DNIS stand for?</t>
+          <t>What does FCR stand for in contact-centre KPIs?</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dialed Number Identification Service</t>
+          <t>First Call Resolution</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barge-In</t>
+          <t>Full Customer Refund</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Text To Speech</t>
+          <t>Fast Cash Reversal</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Voice User Interface</t>
+          <t>Fraud Case Review</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2853,1292 +2909,41 @@
       <c r="K41" t="n">
         <v>1000</v>
       </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bank-260703-140125</t>
+          <t>import-260704-191455</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>subjective</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Which statement about TTS is TRUE?</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>TTS means: converting text into spoken audio prompts</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>TTS means: share of callers pressing to leave the IVR for an agent</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>TTS means: identifying which number the caller dialled</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>TTS means: customer record opening automatically as the call arrives</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>Describe what you see in the compliance slide.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>subjective</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>A VIP customer got wrong information yesterday. Draft your callback opening line.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>45</v>
-      </c>
-      <c r="K43" t="n">
         <v>300</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>What does IVR stand for?</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Interactive Voice Response</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Natural Language Understanding (IVR)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Barge-In</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Menu Depth</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>20</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>What does SPOP stand for?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Skill Based Routing</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Automatic Number Identification</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Dialed Number Identification Service</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Screen Pop</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>20</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Barge-in in an IVR means:</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Callers can respond before the prompt finishes</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>IVR hanging up on silence</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Supervisors joining calls</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Agents interrupting customers</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>25</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Which term matches this definition: “extracting caller intent from free speech instead of menus”?</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>NLUI (Natural Language Understanding (IVR))</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>TTS (Text To Speech)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>CCB (Courtesy Callback)</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>SBR (Skill Based Routing)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>20</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>What does ANI stand for?</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Automatic Number Identification</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Barge-In</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Opt-Out Rate</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Courtesy Callback</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>20</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Which term matches this definition: “caller's phone number captured automatically”?</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>IVR (Interactive Voice Response)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VUI (Voice User Interface)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>ANI (Automatic Number Identification)</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>SPOP (Screen Pop)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>20</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>7</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Which term matches this definition: “share of callers pressing to leave the IVR for an agent”?</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>DTMF (Dual Tone Multi Frequency)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>SBR (Skill Based Routing)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>OPTR (Opt-Out Rate)</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>IVR (Interactive Voice Response)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>20</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>What does TTS stand for?</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Voice User Interface</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Skill Based Routing</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Automatic Call Distributor</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Text To Speech</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>20</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>bank-260703-140439</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Which term matches this definition: “customer record opening automatically as the call arrives”?</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SPOP (Screen Pop)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>ASR (Automatic Speech Recognition)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>MDEP (Menu Depth)</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>DTMF (Dual Tone Multi Frequency)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>20</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>bank-260703-141304</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>What does VUI stand for?</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Dual Tone Multi Frequency</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Voice User Interface</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Courtesy Callback</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Skill Based Routing</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>20</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>bank-260703-141304</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>subjective</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>An elderly customer struggles with the mobile app. How would you help without pushing them away from digital?</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>45</v>
-      </c>
-      <c r="K54" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>bank-260703-141304</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Which term matches this definition: “caller's phone number captured automatically”?</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>IVR (Interactive Voice Response)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>VUI (Voice User Interface)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>ANI (Automatic Number Identification)</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SPOP (Screen Pop)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>20</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>bank-260703-141304</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>A caller says 'I lost my debit card' to the open-ended IVR prompt. Which technology maps this to the card-block flow?</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>DTMF</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Text To Speech</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Screen pop</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Natural Language Understanding</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>25</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>bank-260703-141304</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>4</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>What does OPTR stand for?</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Voice User Interface</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Courtesy Callback</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Menu Depth</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Opt-Out Rate</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>20</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>An agent handled 40 calls with total talk 7240s, hold 1400s and ACW 1240s. AHT in seconds = ?</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>232 sec</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>217 sec</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>307 sec</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>247 sec</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>30</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2500 calls were offered and 345 callers hung up before answer. What is the abandonment rate?</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>28.8%</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>17.3%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>13.8%</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>30</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1400 calls were offered and 60 callers hung up before answer. What is the abandonment rate?</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>12.8%</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>30</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>3</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>600 calls were offered and 43 callers hung up before answer. What is the abandonment rate?</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>7.2%</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>30</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>The IVR handled 1700 calls; 664 completed without reaching an agent. Containment rate = ?</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>44.1%</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>36.6%</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>39.1%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>42.1%</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>30</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>5</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>What does NLUI stand for?</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Screen Pop</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Skill Based Routing</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Natural Language Understanding (IVR)</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Dialed Number Identification Service</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>20</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>6</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>900 calls were offered and 62 callers hung up before answer. What is the abandonment rate?</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>11.9%</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>30</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>7</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>An agent was scheduled 144 hours this month; 36 hours went to leave, training and breaks. Shrinkage = ?</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>30</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>8</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>In an NPS survey, 56% were promoters, 5% detractors and the rest passives. NPS = ?</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>30</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>bank-260703-143043</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>9</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>What does ANI stand for?</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Automatic Number Identification</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Barge-In</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Opt-Out Rate</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Courtesy Callback</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>20</v>
-      </c>
-      <c r="K67" t="n">
-        <v>1000</v>
-      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
